--- a/Distribucion/Excels/CARBAYIN_capacidad.xlsx
+++ b/Distribucion/Excels/CARBAYIN_capacidad.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\Información sobre la capacidad para generación en la red de EdC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\OneDrive - VINCI Energies\SEE\Datos\Distribucion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3C7BA6-2629-41E2-B716-C7D6C3ED134F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AB5327-C1B3-4B96-A7A0-6CD1C4560595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{145218C3-B5CA-4143-AFE4-862602D62B81}"/>
   </bookViews>
   <sheets>
-    <sheet name="Generación" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
